--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -34,79 +34,79 @@
     <t>vr_tot</t>
   </si>
   <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
+    <t>sample_num</t>
   </si>
   <si>
     <t>qg_tot</t>
   </si>
   <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>26158.85 (26860.10 &gt; 2.56%)</t>
-  </si>
-  <si>
-    <t>2.01 (2.45)</t>
-  </si>
-  <si>
-    <t>26171.21 (26860.10 &gt; 2.50%)</t>
-  </si>
-  <si>
-    <t>2.00 (2.45)</t>
-  </si>
-  <si>
-    <t>25113.60 (26860.10 &gt; 6.27%)</t>
-  </si>
-  <si>
-    <t>-0.37 (2.45)</t>
-  </si>
-  <si>
-    <t>25362.42 (26860.10 &gt; 5.73%)</t>
-  </si>
-  <si>
-    <t>-0.31 (2.45)</t>
+    <t>26365.77 (27073.16 &gt; 2.61%)</t>
+  </si>
+  <si>
+    <t>2.00 (245.00)</t>
+  </si>
+  <si>
+    <t>26377.67 (27073.16 &gt; 2.57%)</t>
+  </si>
+  <si>
+    <t>25252.56 (27073.16 &gt; 6.72%)</t>
+  </si>
+  <si>
+    <t>-0.37 (245.00)</t>
+  </si>
+  <si>
+    <t>25464.45 (27073.16 &gt; 5.94%)</t>
+  </si>
+  <si>
+    <t>-0.32 (245.00)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -489,16 +489,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.00129459542222321</v>
+        <v>0.00127012562006712</v>
       </c>
       <c r="C2">
-        <v>0.001294616376981139</v>
+        <v>0.001270140171982348</v>
       </c>
       <c r="D2">
-        <v>3.949136225855909E-05</v>
+        <v>3.923053736798465E-05</v>
       </c>
       <c r="E2">
-        <v>0.0001015072339214385</v>
+        <v>0.0001022720389300957</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -506,33 +506,33 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.02397118860936658</v>
+        <v>0.006624088538717915</v>
       </c>
       <c r="C3">
-        <v>0.0239709127580876</v>
+        <v>0.00662415018721143</v>
       </c>
       <c r="D3">
-        <v>0.004653679672628641</v>
+        <v>0.001428699935786426</v>
       </c>
       <c r="E3">
-        <v>0.01970949582755566</v>
+        <v>0.004680263344198465</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.06301460992386737</v>
+      </c>
+      <c r="C4">
+        <v>0.06301527721074102</v>
+      </c>
+      <c r="D4">
+        <v>0.0182597991079092</v>
+      </c>
+      <c r="E4">
+        <v>0.01620936952531338</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -540,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.0006311949109658599</v>
+        <v>0.1398116052150726</v>
       </c>
       <c r="C5">
-        <v>0.000631194154266268</v>
+        <v>0.1398079097270966</v>
       </c>
       <c r="D5">
-        <v>3.859590651700273E-05</v>
+        <v>0.08751530945301056</v>
       </c>
       <c r="E5">
-        <v>9.70006876741536E-05</v>
+        <v>0.06060534343123436</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,16 +557,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.06231207237088932</v>
+        <v>0.1298364507118613</v>
       </c>
       <c r="C6">
-        <v>0.06231283111141763</v>
+        <v>0.1298326267109329</v>
       </c>
       <c r="D6">
-        <v>0.0182630717754364</v>
+        <v>0.08744769543409348</v>
       </c>
       <c r="E6">
-        <v>0.01584559492766857</v>
+        <v>0.06011797487735748</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -590,17 +590,17 @@
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,16 +608,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.06228584556776383</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.06228661132155742</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.018387695774436</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.01583132706582546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -625,16 +625,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.01297804340720177</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.01297861244529486</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>6.701495294691995E-05</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.0001662660215515643</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -642,33 +642,33 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.01297187898308039</v>
+        <v>0.002618875271016839</v>
       </c>
       <c r="C11">
-        <v>0.01297240983694792</v>
+        <v>0.00406339853900806</v>
       </c>
       <c r="D11">
-        <v>6.732678593834862E-05</v>
+        <v>0.1664232015609741</v>
       </c>
       <c r="E11">
-        <v>0.0001627961901249364</v>
+        <v>0.5311644077301025</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
-        <v>0.002575719791465673</v>
-      </c>
-      <c r="C12">
-        <v>0.003952470244985219</v>
-      </c>
-      <c r="D12">
-        <v>0.1695405542850494</v>
-      </c>
-      <c r="E12">
-        <v>0.5202538371086121</v>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -676,16 +676,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.006728140652283681</v>
+        <v>0.0006201962241902947</v>
       </c>
       <c r="C13">
-        <v>0.006728157008292488</v>
+        <v>0.0006201954674907029</v>
       </c>
       <c r="D13">
-        <v>0.001472583971917629</v>
+        <v>3.831729918601923E-05</v>
       </c>
       <c r="E13">
-        <v>0.004512378480285406</v>
+        <v>9.766809671418741E-05</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -693,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.00664870510879414</v>
+        <v>0.06303562593430212</v>
       </c>
       <c r="C14">
-        <v>0.006648719916356655</v>
+        <v>0.06303628529924118</v>
       </c>
       <c r="D14">
-        <v>0.001428365707397461</v>
+        <v>0.01813553832471371</v>
       </c>
       <c r="E14">
-        <v>0.004507509060204029</v>
+        <v>0.01622333377599716</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,33 +710,33 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.4497597217559814</v>
+        <v>0.06529642641544342</v>
       </c>
       <c r="C15">
-        <v>0.4497597217559814</v>
+        <v>0.06529659032821655</v>
       </c>
       <c r="D15">
-        <v>0.03090240806341171</v>
+        <v>0.004609644878655672</v>
       </c>
       <c r="E15">
-        <v>0.08447970449924469</v>
+        <v>0.0228151697665453</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.06485083699226379</v>
-      </c>
-      <c r="C16">
-        <v>0.06485091894865036</v>
-      </c>
-      <c r="D16">
-        <v>0.004582539666444063</v>
-      </c>
-      <c r="E16">
-        <v>0.02189953811466694</v>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,16 +744,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.128423223470702</v>
+        <v>0.006701967227009311</v>
       </c>
       <c r="C17">
-        <v>0.1284195881116044</v>
+        <v>0.006702030062409126</v>
       </c>
       <c r="D17">
-        <v>0.08806665241718292</v>
+        <v>0.001472171978093684</v>
       </c>
       <c r="E17">
-        <v>0.05892320349812508</v>
+        <v>0.004683846607804298</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -761,33 +761,38 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.1380849033594131</v>
+        <v>0.02388846557568142</v>
       </c>
       <c r="C18">
-        <v>0.1380813270807266</v>
+        <v>0.02388833002427239</v>
       </c>
       <c r="D18">
-        <v>0.0881306529045105</v>
+        <v>0.004657984245568514</v>
       </c>
       <c r="E18">
-        <v>0.05933037027716637</v>
+        <v>0.02047858387231827</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.4573389887809753</v>
+      </c>
+      <c r="C20">
+        <v>0.4573389887809753</v>
+      </c>
+      <c r="D20">
+        <v>0.03105659037828445</v>
+      </c>
+      <c r="E20">
+        <v>0.08785603940486908</v>
       </c>
     </row>
   </sheetData>
